--- a/data/excel/kof_indicator_economic_sentiment.xlsx
+++ b/data/excel/kof_indicator_economic_sentiment.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C496"/>
+  <dimension ref="A1:C497"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -497,7 +497,7 @@
         <v>1986-02</v>
       </c>
       <c r="C15">
-        <v>98.2</v>
+        <v>98.1</v>
       </c>
     </row>
     <row r="16">
@@ -577,7 +577,7 @@
         <v>1986-12</v>
       </c>
       <c r="C25">
-        <v>100.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -737,7 +737,7 @@
         <v>1988-08</v>
       </c>
       <c r="C45">
-        <v>108.8</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="46">
@@ -769,7 +769,7 @@
         <v>1988-12</v>
       </c>
       <c r="C49">
-        <v>111.6</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="50">
@@ -977,7 +977,7 @@
         <v>1991-02</v>
       </c>
       <c r="C75">
-        <v>96.5</v>
+        <v>96.4</v>
       </c>
     </row>
     <row r="76">
@@ -1009,7 +1009,7 @@
         <v>1991-06</v>
       </c>
       <c r="C79">
-        <v>95</v>
+        <v>95.1</v>
       </c>
     </row>
     <row r="80">
@@ -1017,7 +1017,7 @@
         <v>1991-07</v>
       </c>
       <c r="C80">
-        <v>93</v>
+        <v>93.1</v>
       </c>
     </row>
     <row r="81">
@@ -1073,7 +1073,7 @@
         <v>1992-02</v>
       </c>
       <c r="C87">
-        <v>92.9</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="88">
@@ -1297,7 +1297,7 @@
         <v>1994-06</v>
       </c>
       <c r="C115">
-        <v>96.5</v>
+        <v>96.6</v>
       </c>
     </row>
     <row r="116">
@@ -1417,7 +1417,7 @@
         <v>1995-09</v>
       </c>
       <c r="C130">
-        <v>101.5</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="131">
@@ -1681,7 +1681,7 @@
         <v>1998-06</v>
       </c>
       <c r="C163">
-        <v>112.1</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="164">
@@ -1833,7 +1833,7 @@
         <v>2000-01</v>
       </c>
       <c r="C182">
-        <v>115</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="183">
@@ -1881,7 +1881,7 @@
         <v>2000-07</v>
       </c>
       <c r="C188">
-        <v>116.7</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="189">
@@ -1961,7 +1961,7 @@
         <v>2001-05</v>
       </c>
       <c r="C198">
-        <v>101.6</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="199">
@@ -1993,7 +1993,7 @@
         <v>2001-09</v>
       </c>
       <c r="C202">
-        <v>95.3</v>
+        <v>95.4</v>
       </c>
     </row>
     <row r="203">
@@ -2073,7 +2073,7 @@
         <v>2002-07</v>
       </c>
       <c r="C212">
-        <v>94.9</v>
+        <v>95</v>
       </c>
     </row>
     <row r="213">
@@ -2297,7 +2297,7 @@
         <v>2004-11</v>
       </c>
       <c r="C240">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="241">
@@ -2686,7 +2686,7 @@
         <v>110.82333148471584</v>
       </c>
       <c r="C283">
-        <v>95.3</v>
+        <v>95.4</v>
       </c>
     </row>
     <row r="284">
@@ -2796,7 +2796,7 @@
         <v>75.48178180158092</v>
       </c>
       <c r="C293">
-        <v>69.3</v>
+        <v>69.4</v>
       </c>
     </row>
     <row r="294">
@@ -2807,7 +2807,7 @@
         <v>78.33750569028717</v>
       </c>
       <c r="C294">
-        <v>73.6</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="295">
@@ -3049,7 +3049,7 @@
         <v>114.55529824615189</v>
       </c>
       <c r="C316">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="317">
@@ -3071,7 +3071,7 @@
         <v>112.59367180754332</v>
       </c>
       <c r="C318">
-        <v>102.1</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="319">
@@ -3181,7 +3181,7 @@
         <v>101.6601963687906</v>
       </c>
       <c r="C328">
-        <v>92.8</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="329">
@@ -3423,7 +3423,7 @@
         <v>107.16456611046436</v>
       </c>
       <c r="C350">
-        <v>98.9</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="351">
@@ -3467,7 +3467,7 @@
         <v>105.73935693527974</v>
       </c>
       <c r="C354">
-        <v>99.6</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="355">
@@ -3566,7 +3566,7 @@
         <v>95.89649731294965</v>
       </c>
       <c r="C363">
-        <v>101.4</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="364">
@@ -3577,7 +3577,7 @@
         <v>97.91268698265425</v>
       </c>
       <c r="C364">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="365">
@@ -3588,7 +3588,7 @@
         <v>96.98304005586688</v>
       </c>
       <c r="C365">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="366">
@@ -3621,7 +3621,7 @@
         <v>94.60878394168292</v>
       </c>
       <c r="C368">
-        <v>103.1</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="369">
@@ -3676,7 +3676,7 @@
         <v>94.88421273678824</v>
       </c>
       <c r="C373">
-        <v>105.6</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="374">
@@ -3764,7 +3764,7 @@
         <v>96.58642449883986</v>
       </c>
       <c r="C381">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="382">
@@ -3830,7 +3830,7 @@
         <v>100.65702097150987</v>
       </c>
       <c r="C387">
-        <v>108.7</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="388">
@@ -3841,7 +3841,7 @@
         <v>101.41790805934052</v>
       </c>
       <c r="C388">
-        <v>109.2</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="389">
@@ -3852,7 +3852,7 @@
         <v>101.31167457792358</v>
       </c>
       <c r="C389">
-        <v>110.2</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="390">
@@ -3940,7 +3940,7 @@
         <v>107.22459733922214</v>
       </c>
       <c r="C397">
-        <v>115.8</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="398">
@@ -3984,7 +3984,7 @@
         <v>107.05282683508693</v>
       </c>
       <c r="C401">
-        <v>113.5</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="402">
@@ -3995,7 +3995,7 @@
         <v>108.13067757188846</v>
       </c>
       <c r="C402">
-        <v>111.7</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="403">
@@ -4105,7 +4105,7 @@
         <v>103.45544861344516</v>
       </c>
       <c r="C412">
-        <v>107</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="413">
@@ -4138,7 +4138,7 @@
         <v>100.82250766582462</v>
       </c>
       <c r="C415">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="416">
@@ -4149,7 +4149,7 @@
         <v>101.60895553793254</v>
       </c>
       <c r="C416">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="417">
@@ -4193,7 +4193,7 @@
         <v>100.16517103860673</v>
       </c>
       <c r="C420">
-        <v>103.1</v>
+        <v>103</v>
       </c>
     </row>
     <row r="421">
@@ -4248,7 +4248,7 @@
         <v>64.42052514017863</v>
       </c>
       <c r="C425">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="426">
@@ -4281,7 +4281,7 @@
         <v>85.76966409798834</v>
       </c>
       <c r="C428">
-        <v>83</v>
+        <v>83.1</v>
       </c>
     </row>
     <row r="429">
@@ -4292,7 +4292,7 @@
         <v>88.84108647111391</v>
       </c>
       <c r="C429">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="430">
@@ -4369,7 +4369,7 @@
         <v>98.62584313883315</v>
       </c>
       <c r="C436">
-        <v>103.1</v>
+        <v>103</v>
       </c>
     </row>
     <row r="437">
@@ -4380,7 +4380,7 @@
         <v>106.21300358263508</v>
       </c>
       <c r="C437">
-        <v>105.7</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="438">
@@ -4391,7 +4391,7 @@
         <v>107.97218096343971</v>
       </c>
       <c r="C438">
-        <v>110.6</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="439">
@@ -4402,7 +4402,7 @@
         <v>109.95870038295018</v>
       </c>
       <c r="C439">
-        <v>116.2</v>
+        <v>116.3</v>
       </c>
     </row>
     <row r="440">
@@ -4413,7 +4413,7 @@
         <v>113.91284496028362</v>
       </c>
       <c r="C440">
-        <v>118.5</v>
+        <v>118.6</v>
       </c>
     </row>
     <row r="441">
@@ -4435,7 +4435,7 @@
         <v>115.12174034990774</v>
       </c>
       <c r="C442">
-        <v>118.8</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="443">
@@ -4457,7 +4457,7 @@
         <v>114.04510720897999</v>
       </c>
       <c r="C444">
-        <v>117.5</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="445">
@@ -4490,7 +4490,7 @@
         <v>113.15045936215607</v>
       </c>
       <c r="C447">
-        <v>114.7</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="448">
@@ -4501,7 +4501,7 @@
         <v>113.2389253049668</v>
       </c>
       <c r="C448">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="449">
@@ -4512,7 +4512,7 @@
         <v>105.53247405392855</v>
       </c>
       <c r="C449">
-        <v>104.6</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="450">
@@ -4523,7 +4523,7 @@
         <v>104.42404168299124</v>
       </c>
       <c r="C450">
-        <v>104.9</v>
+        <v>105</v>
       </c>
     </row>
     <row r="451">
@@ -4556,7 +4556,7 @@
         <v>95.40166104727534</v>
       </c>
       <c r="C453">
-        <v>98</v>
+        <v>98.1</v>
       </c>
     </row>
     <row r="454">
@@ -4600,7 +4600,7 @@
         <v>90.0048810598271</v>
       </c>
       <c r="C457">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="458">
@@ -4611,7 +4611,7 @@
         <v>92.92815195061405</v>
       </c>
       <c r="C458">
-        <v>97.6</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="459">
@@ -4622,7 +4622,7 @@
         <v>93.33782535221474</v>
       </c>
       <c r="C459">
-        <v>97.4</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="460">
@@ -4633,7 +4633,7 @@
         <v>92.98954895747072</v>
       </c>
       <c r="C460">
-        <v>97.1</v>
+        <v>97</v>
       </c>
     </row>
     <row r="461">
@@ -4644,7 +4644,7 @@
         <v>89.70073282448473</v>
       </c>
       <c r="C461">
-        <v>97.5</v>
+        <v>97.6</v>
       </c>
     </row>
     <row r="462">
@@ -4655,7 +4655,7 @@
         <v>87.11860496848924</v>
       </c>
       <c r="C462">
-        <v>95.8</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="463">
@@ -4666,7 +4666,7 @@
         <v>88.48533681964884</v>
       </c>
       <c r="C463">
-        <v>95</v>
+        <v>95.1</v>
       </c>
     </row>
     <row r="464">
@@ -4677,7 +4677,7 @@
         <v>87.17433771128724</v>
       </c>
       <c r="C464">
-        <v>94.5</v>
+        <v>94.6</v>
       </c>
     </row>
     <row r="465">
@@ -4688,7 +4688,7 @@
         <v>87.85845951929474</v>
       </c>
       <c r="C465">
-        <v>93.8</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="466">
@@ -4732,7 +4732,7 @@
         <v>81.92409806849318</v>
       </c>
       <c r="C469">
-        <v>96.4</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="470">
@@ -4743,7 +4743,7 @@
         <v>84.8596141864255</v>
       </c>
       <c r="C470">
-        <v>95.9</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="471">
@@ -4754,7 +4754,7 @@
         <v>86.29972076295952</v>
       </c>
       <c r="C471">
-        <v>95.4</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="472">
@@ -4765,7 +4765,7 @@
         <v>86.2596538786517</v>
       </c>
       <c r="C472">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="473">
@@ -4776,7 +4776,7 @@
         <v>87.79075203947039</v>
       </c>
       <c r="C473">
-        <v>96.5</v>
+        <v>96.6</v>
       </c>
     </row>
     <row r="474">
@@ -4787,7 +4787,7 @@
         <v>88.62441125920739</v>
       </c>
       <c r="C474">
-        <v>96.5</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="475">
@@ -4798,7 +4798,7 @@
         <v>89.01456761885908</v>
       </c>
       <c r="C475">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="476">
@@ -4809,7 +4809,7 @@
         <v>91.52885614846379</v>
       </c>
       <c r="C476">
-        <v>96.5</v>
+        <v>96.6</v>
       </c>
     </row>
     <row r="477">
@@ -4864,7 +4864,7 @@
         <v>92.25192294776953</v>
       </c>
       <c r="C481">
-        <v>94.7</v>
+        <v>94.6</v>
       </c>
     </row>
     <row r="482">
@@ -4875,7 +4875,7 @@
         <v>91.9095149036078</v>
       </c>
       <c r="C482">
-        <v>95.9</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="483">
@@ -4886,7 +4886,7 @@
         <v>92.22749758925639</v>
       </c>
       <c r="C483">
-        <v>97.1</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="484">
@@ -4897,7 +4897,7 @@
         <v>89.21378339151555</v>
       </c>
       <c r="C484">
-        <v>96.1</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="485">
@@ -4908,7 +4908,7 @@
         <v>89.90874125465442</v>
       </c>
       <c r="C485">
-        <v>94.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="486">
@@ -4919,7 +4919,7 @@
         <v>89.68645705181304</v>
       </c>
       <c r="C486">
-        <v>95.5</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="487">
@@ -4930,7 +4930,7 @@
         <v>90.85083187338323</v>
       </c>
       <c r="C487">
-        <v>94.6</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="488">
@@ -4941,7 +4941,7 @@
         <v>93.38026170902224</v>
       </c>
       <c r="C488">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="489">
@@ -4952,7 +4952,7 @@
         <v>88.12489179212739</v>
       </c>
       <c r="C489">
-        <v>95.5</v>
+        <v>95.6</v>
       </c>
     </row>
     <row r="490">
@@ -4996,7 +4996,7 @@
         <v>92.9176482319737</v>
       </c>
       <c r="C493">
-        <v>97.2</v>
+        <v>97.1</v>
       </c>
     </row>
     <row r="494">
@@ -5007,7 +5007,7 @@
         <v>95.78389307933546</v>
       </c>
       <c r="C494">
-        <v>99.2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="495">
@@ -5018,7 +5018,7 @@
         <v>94.99905041160949</v>
       </c>
       <c r="C495">
-        <v>98.2</v>
+        <v>97.9</v>
       </c>
     </row>
     <row r="496">
@@ -5026,12 +5026,20 @@
         <v>2026-03</v>
       </c>
       <c r="C496">
-        <v>96.7</v>
+        <v>96.4</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="C497">
+        <v>93.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C496"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C497"/>
   </ignoredErrors>
 </worksheet>
 </file>